--- a/data/trans_orig/IP07KS_C09_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C09_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ir bien en el colegio en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de ir bien en el colegio, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51109</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41248</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60647</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35180</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27869</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42168</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50805</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40330</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59832</t>
+          <t>44845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>88417</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>76565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98327</t>
+          <t>98917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36015</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27621</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45570</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30294</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23677</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37610</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36480</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>67816</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78087</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13711</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7521</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6825</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2646</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2359</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97854</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97854</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97854</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>98615</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>98615</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>98615</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>166540</t>
+          <t>169460</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166540</t>
+          <t>169460</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>166540</t>
+          <t>169460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88580</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74309</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106086</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55834</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28799</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73295</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>60396</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74320</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108387</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>145359</t>
+          <t>148976</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106511</t>
+          <t>131291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170892</t>
+          <t>168051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54879</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67647</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>45447</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24540</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58796</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41253</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>58595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>99380</t>
+          <t>102735</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73936</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119946</t>
+          <t>118344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23334</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>38084</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11933</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84301</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>26,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24174</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>62258</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127010</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>139688</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>122386</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>159358</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>91014</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>60109</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>109311</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>97705</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>85497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161101</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>231345</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188453</t>
+          <t>214525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257901</t>
+          <t>261113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>90894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75412</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104945</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>75741</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47941</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93094</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>91663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>166154</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>148413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188261</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31227</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20595</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>48641</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12588</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>101484</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>72730</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7707</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,27 +2611,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>271397</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>271397</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>271397</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>576</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
